--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoInfo.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>销售单号</t>
   </si>
@@ -159,6 +172,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>客户PO号</t>
   </si>
   <si>
     <t>明细备注</t>
@@ -328,6 +344,9 @@
     <t>{.remark}</t>
   </si>
   <si>
+    <t>{.customerPO}</t>
+  </si>
+  <si>
     <t>{.detailRemark}</t>
   </si>
   <si>
@@ -343,7 +362,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1314,7 +1333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AU3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -1329,11 +1348,11 @@
     <col min="26" max="29" width="22.5" style="1" customWidth="1"/>
     <col min="30" max="32" width="20.125" customWidth="1"/>
     <col min="33" max="33" width="28.375" customWidth="1"/>
-    <col min="34" max="42" width="20.125" customWidth="1"/>
-    <col min="43" max="46" width="20.625" customWidth="1"/>
+    <col min="34" max="43" width="20.125" customWidth="1"/>
+    <col min="44" max="47" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46">
+    <row r="1" spans="1:47">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1472,145 +1491,151 @@
       <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="AU1" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:46">
+    <row r="2" spans="1:47">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="3:3">
